--- a/137558_Cuenca_Chancay_-_Huaral/_raw_reportes_xlsx/IDConfig_64997_completo.xlsx
+++ b/137558_Cuenca_Chancay_-_Huaral/_raw_reportes_xlsx/IDConfig_64997_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3be9cd84b5c24004"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R775acb3080b54a98"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9411</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9762</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0240</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0489</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9160</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0006</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0598</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1325</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6357</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/137558_Cuenca_Chancay_-_Huaral/_raw_reportes_xlsx/IDConfig_64997_completo.xlsx
+++ b/137558_Cuenca_Chancay_-_Huaral/_raw_reportes_xlsx/IDConfig_64997_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R775acb3080b54a98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb1b014ce65c84313"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1882</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2654</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1808</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8329</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8443</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0474</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2192</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2169</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2536</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2302</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4374</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.3392</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9162</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8456</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.3519</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1994</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9451</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8806</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5544</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6921</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6453</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7632</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8329</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8934</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8921</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8458</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8573</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8809</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9957</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7513</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7236</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7401</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6804</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8817</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
